--- a/docs/modelos_importacao/06_Exemplo_Historico_Premios_36_Meses_TESTE.xlsx
+++ b/docs/modelos_importacao/06_Exemplo_Historico_Premios_36_Meses_TESTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prémios'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prémios'!$A$1:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leia-me'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -477,13 +478,13 @@
         <v>44927</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45291</v>
+        <v>44957</v>
       </c>
       <c r="C2" t="n">
-        <v>960000</v>
+        <v>220000</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,16 +494,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45292</v>
+        <v>44958</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45657</v>
+        <v>44985</v>
       </c>
       <c r="C3" t="n">
-        <v>1032000</v>
+        <v>220000</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -512,25 +513,652 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45016</v>
+      </c>
+      <c r="C4" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45046</v>
+      </c>
+      <c r="C5" t="n">
+        <v>231000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45077</v>
+      </c>
+      <c r="C6" t="n">
+        <v>231000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="C7" t="n">
+        <v>231000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45138</v>
+      </c>
+      <c r="C8" t="n">
+        <v>242000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="C9" t="n">
+        <v>242000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="C10" t="n">
+        <v>242000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C11" t="n">
+        <v>253000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C12" t="n">
+        <v>253000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="C13" t="n">
+        <v>253000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45322</v>
+      </c>
+      <c r="C14" t="n">
+        <v>285120</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C15" t="n">
+        <v>285120</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="C16" t="n">
+        <v>285120</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="C17" t="n">
+        <v>297000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="C18" t="n">
+        <v>297000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C19" t="n">
+        <v>297000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45504</v>
+      </c>
+      <c r="C20" t="n">
+        <v>308880</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45535</v>
+      </c>
+      <c r="C21" t="n">
+        <v>308880</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="C22" t="n">
+        <v>308880</v>
+      </c>
+      <c r="D22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="C23" t="n">
+        <v>320760</v>
+      </c>
+      <c r="D23" t="n">
+        <v>27</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="C24" t="n">
+        <v>320760</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C25" t="n">
+        <v>320760</v>
+      </c>
+      <c r="D25" t="n">
+        <v>27</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B26" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C26" t="n">
+        <v>359251.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>28</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="C27" t="n">
+        <v>359251.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>28</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C28" t="n">
+        <v>359251.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>28</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="C29" t="n">
+        <v>372081.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>29</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="C30" t="n">
+        <v>372081.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C31" t="n">
+        <v>372081.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="C32" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="C33" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D33" t="n">
+        <v>30</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C34" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C35" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C36" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C4" t="n">
-        <v>1110000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C37" t="n">
+        <v>384912</v>
+      </c>
+      <c r="D37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>AOA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -568,7 +1196,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Prémios fictícios correspondentes ao período de 2023–2025.</t>
+          <t>Prémios mensais fictícios de Janeiro de 2023 a Dezembro de 2025 (36 períodos).</t>
         </is>
       </c>
     </row>
@@ -592,7 +1220,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Valores assumem quatro pessoas seguras.</t>
+          <t>Cresce de 20 para 30 pessoas seguras, como no exemplo de membros.</t>
         </is>
       </c>
     </row>
